--- a/data/raw/FORMATOS RA CICLO UNO RC/FormatoRA_EspGerMercadeo_VNAL.xlsx
+++ b/data/raw/FORMATOS RA CICLO UNO RC/FormatoRA_EspGerMercadeo_VNAL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/micortes_poligran_edu_co/Documents/Escritorio/FORMATOS RA CICLO UNO RC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Analisis_Curricular/data/raw/FORMATOS RA CICLO UNO RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{4A644C99-43BB-4A2D-A390-707205923635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADEAC43E-9562-4837-839F-5A2EDD015267}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="4" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
   </bookViews>
   <sheets>
     <sheet name="Paso1 Analisis perfil egreso" sheetId="1" r:id="rId1"/>
@@ -3696,15 +3696,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3713,22 +3704,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3742,6 +3724,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3776,6 +3776,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3783,12 +3789,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -8509,21 +8509,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FA7EDF-246F-4EE0-BFE4-7EACACD45C48}">
   <dimension ref="A1:K28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="76.26953125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="76.21875" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" style="3" customWidth="1"/>
-    <col min="3" max="4" width="69.1796875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="34.1796875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="34.1796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" style="3" customWidth="1"/>
+    <col min="3" max="4" width="69.21875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="34.21875" style="3" customWidth="1"/>
+    <col min="6" max="7" width="34.21875" style="1" customWidth="1"/>
     <col min="8" max="8" width="87" style="3" customWidth="1"/>
-    <col min="9" max="9" width="95.26953125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="67.1796875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="76.81640625" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="76.26953125" style="3"/>
+    <col min="9" max="9" width="95.21875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="67.21875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="76.77734375" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="76.21875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="42.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" ht="42" x14ac:dyDescent="0.5">
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
@@ -8585,7 +8585,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="6" customFormat="1" ht="77.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" s="6" customFormat="1" ht="77.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="73" t="s">
         <v>18</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="6" customFormat="1" ht="77.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" s="6" customFormat="1" ht="77.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="73"/>
       <c r="B4" s="73"/>
       <c r="C4" s="76"/>
@@ -8639,7 +8639,7 @@
       <c r="J4" s="76"/>
       <c r="K4" s="76"/>
     </row>
-    <row r="5" spans="1:11" s="5" customFormat="1" ht="113.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" s="5" customFormat="1" ht="113.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="73"/>
       <c r="B5" s="73"/>
       <c r="C5" s="76"/>
@@ -8800,16 +8800,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="E1:G1"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="I3:I5"/>
     <mergeCell ref="J3:J5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="E1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8820,16 +8820,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C1850E-A9C8-4F69-8E80-DEAF9721FFBF}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="19" style="3" customWidth="1"/>
     <col min="2" max="2" width="24" style="3" customWidth="1"/>
-    <col min="3" max="3" width="32.1796875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="36.81640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="41.54296875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="96.81640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="27.81640625" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="11.453125" style="3"/>
+    <col min="3" max="3" width="32.21875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="36.77734375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="41.5546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="96.77734375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="27.77734375" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.5">
@@ -8843,7 +8843,7 @@
       <c r="F1" s="100"/>
       <c r="G1" s="100"/>
     </row>
-    <row r="2" spans="1:7" ht="65" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.5">
       <c r="A2" s="44" t="s">
         <v>35</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="5" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" s="5" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -8912,7 +8912,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="5" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" s="5" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>2</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="5" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" s="5" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>3</v>
       </c>
@@ -9009,22 +9009,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AAF649-42F4-466A-BE11-44357078F961}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="81.1796875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="28.1796875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="17.54296875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="17.81640625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="20.1796875" style="8" customWidth="1"/>
-    <col min="8" max="8" width="18.26953125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="81.21875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="28.21875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="17.77734375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="20.21875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" style="1" customWidth="1"/>
     <col min="9" max="9" width="72" style="1" customWidth="1"/>
-    <col min="10" max="10" width="43.26953125" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="11.453125" style="6"/>
+    <col min="10" max="10" width="43.21875" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="78" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="84" x14ac:dyDescent="0.3">
       <c r="A1" s="35" t="s">
         <v>57</v>
       </c>
@@ -9053,7 +9053,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="38" t="s">
         <v>66</v>
       </c>
@@ -9082,7 +9082,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="66" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
         <v>50</v>
       </c>
@@ -9111,7 +9111,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>50</v>
       </c>
@@ -9140,7 +9140,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>50</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
         <v>53</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="66" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>53</v>
       </c>
@@ -9227,7 +9227,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>53</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
         <v>55</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>55</v>
       </c>
@@ -9314,7 +9314,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A11" s="26" t="s">
         <v>55</v>
       </c>
@@ -9391,18 +9391,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F726B80-E6B4-4ED4-A764-E59AF4E18393}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="57.1796875" style="24" customWidth="1"/>
-    <col min="2" max="2" width="43.81640625" style="24" customWidth="1"/>
+    <col min="1" max="1" width="57.21875" style="24" customWidth="1"/>
+    <col min="2" max="2" width="43.77734375" style="24" customWidth="1"/>
     <col min="3" max="3" width="48" style="24" customWidth="1"/>
-    <col min="4" max="4" width="45.81640625" style="24" customWidth="1"/>
-    <col min="5" max="5" width="39.1796875" style="24" customWidth="1"/>
-    <col min="6" max="6" width="33.453125" style="24" customWidth="1"/>
-    <col min="7" max="16384" width="11.453125" style="24"/>
+    <col min="4" max="4" width="45.77734375" style="24" customWidth="1"/>
+    <col min="5" max="5" width="39.21875" style="24" customWidth="1"/>
+    <col min="6" max="6" width="33.44140625" style="24" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="65" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="60" x14ac:dyDescent="0.3">
       <c r="A1" s="35" t="s">
         <v>87</v>
       </c>
@@ -9422,7 +9422,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="38" t="s">
         <v>93</v>
       </c>
@@ -9442,14 +9442,14 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B3" s="78" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="91" t="s">
         <v>100</v>
       </c>
       <c r="D3" s="55" t="s">
@@ -9462,12 +9462,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B4" s="79"/>
-      <c r="C4" s="88"/>
+      <c r="C4" s="92"/>
       <c r="D4" s="25" t="s">
         <v>104</v>
       </c>
@@ -9476,10 +9476,10 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="79"/>
-      <c r="C5" s="88"/>
+      <c r="C5" s="92"/>
       <c r="D5" s="50" t="s">
         <v>105</v>
       </c>
@@ -9488,10 +9488,10 @@
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="26"/>
       <c r="B6" s="80"/>
-      <c r="C6" s="89"/>
+      <c r="C6" s="93"/>
       <c r="D6" s="56" t="s">
         <v>107</v>
       </c>
@@ -9500,14 +9500,14 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B7" s="78" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="87" t="s">
+      <c r="C7" s="91" t="s">
         <v>110</v>
       </c>
       <c r="D7" s="55" t="s">
@@ -9520,12 +9520,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B8" s="79"/>
-      <c r="C8" s="88"/>
+      <c r="C8" s="92"/>
       <c r="D8" s="50" t="s">
         <v>105</v>
       </c>
@@ -9534,10 +9534,10 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="26"/>
       <c r="B9" s="80"/>
-      <c r="C9" s="89"/>
+      <c r="C9" s="93"/>
       <c r="D9" s="25" t="s">
         <v>107</v>
       </c>
@@ -9546,14 +9546,14 @@
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="78" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="87" t="s">
+      <c r="C10" s="91" t="s">
         <v>114</v>
       </c>
       <c r="D10" s="55" t="s">
@@ -9566,12 +9566,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B11" s="79"/>
-      <c r="C11" s="88"/>
+      <c r="C11" s="92"/>
       <c r="D11" s="50" t="s">
         <v>105</v>
       </c>
@@ -9580,10 +9580,10 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="26"/>
       <c r="B12" s="80"/>
-      <c r="C12" s="89"/>
+      <c r="C12" s="93"/>
       <c r="D12" s="25" t="s">
         <v>107</v>
       </c>
@@ -9592,14 +9592,14 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B13" s="78" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="87" t="s">
+      <c r="C13" s="91" t="s">
         <v>117</v>
       </c>
       <c r="D13" s="55" t="s">
@@ -9612,12 +9612,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B14" s="79"/>
-      <c r="C14" s="88"/>
+      <c r="C14" s="92"/>
       <c r="D14" s="50" t="s">
         <v>105</v>
       </c>
@@ -9626,10 +9626,10 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="26"/>
       <c r="B15" s="80"/>
-      <c r="C15" s="89"/>
+      <c r="C15" s="93"/>
       <c r="D15" s="56" t="s">
         <v>107</v>
       </c>
@@ -9638,14 +9638,14 @@
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B16" s="78" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="87" t="s">
+      <c r="C16" s="91" t="s">
         <v>121</v>
       </c>
       <c r="D16" s="55" t="s">
@@ -9658,12 +9658,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B17" s="79"/>
-      <c r="C17" s="88"/>
+      <c r="C17" s="92"/>
       <c r="D17" s="50" t="s">
         <v>105</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="26"/>
       <c r="B18" s="105"/>
       <c r="C18" s="106"/>
@@ -9684,14 +9684,14 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B19" s="78" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="87" t="s">
+      <c r="C19" s="91" t="s">
         <v>124</v>
       </c>
       <c r="D19" s="25" t="s">
@@ -9704,12 +9704,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B20" s="79"/>
-      <c r="C20" s="88"/>
+      <c r="C20" s="92"/>
       <c r="D20" s="25" t="s">
         <v>105</v>
       </c>
@@ -9718,10 +9718,10 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="79"/>
-      <c r="C21" s="88"/>
+      <c r="C21" s="92"/>
       <c r="D21" s="25" t="s">
         <v>126</v>
       </c>
@@ -9730,10 +9730,10 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="32"/>
       <c r="B22" s="80"/>
-      <c r="C22" s="89"/>
+      <c r="C22" s="93"/>
       <c r="D22" s="56" t="s">
         <v>107</v>
       </c>
@@ -9742,14 +9742,14 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B23" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="87" t="s">
+      <c r="C23" s="91" t="s">
         <v>128</v>
       </c>
       <c r="D23" s="25" t="s">
@@ -9762,12 +9762,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B24" s="79"/>
-      <c r="C24" s="88"/>
+      <c r="C24" s="92"/>
       <c r="D24" s="25" t="s">
         <v>105</v>
       </c>
@@ -9776,10 +9776,10 @@
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="26"/>
       <c r="B25" s="80"/>
-      <c r="C25" s="89"/>
+      <c r="C25" s="93"/>
       <c r="D25" s="56" t="s">
         <v>107</v>
       </c>
@@ -9790,18 +9790,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="E19:E22"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
     <mergeCell ref="E3:E6"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="C7:C9"/>
@@ -9811,6 +9799,18 @@
     <mergeCell ref="E10:E12"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="E19:E22"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="C19:C22"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A23:A25 A3:A21" xr:uid="{3809FD9E-C184-4096-95E4-A87EBEFB4EA5}">
@@ -9826,27 +9826,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B248250-C92C-4D02-A0C3-2CB27C341894}">
   <dimension ref="A1:Q33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" style="5" customWidth="1"/>
     <col min="2" max="2" width="57" style="5" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="26.54296875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="26.5546875" style="5" customWidth="1"/>
     <col min="5" max="5" width="57" style="6" customWidth="1"/>
-    <col min="6" max="6" width="27.1796875" style="7" customWidth="1"/>
-    <col min="7" max="7" width="16.7265625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="13.54296875" style="7" customWidth="1"/>
-    <col min="10" max="10" width="20.453125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="24.453125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="11.26953125" style="7" customWidth="1"/>
-    <col min="13" max="14" width="40.7265625" style="6" customWidth="1"/>
-    <col min="15" max="15" width="50.1796875" style="6" customWidth="1"/>
-    <col min="16" max="16" width="69.26953125" style="6" customWidth="1"/>
-    <col min="17" max="16384" width="11.453125" style="5"/>
+    <col min="6" max="6" width="27.21875" style="7" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" style="7" customWidth="1"/>
+    <col min="10" max="10" width="20.44140625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="24.44140625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="11.21875" style="7" customWidth="1"/>
+    <col min="13" max="14" width="40.77734375" style="6" customWidth="1"/>
+    <col min="15" max="15" width="50.21875" style="6" customWidth="1"/>
+    <col min="16" max="16" width="69.21875" style="6" customWidth="1"/>
+    <col min="17" max="16384" width="11.44140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="7" customFormat="1" ht="65" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.3">
       <c r="A1" s="35" t="s">
         <v>129</v>
       </c>
@@ -9865,10 +9865,10 @@
       <c r="F1" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="G1" s="93" t="s">
+      <c r="G1" s="87" t="s">
         <v>135</v>
       </c>
-      <c r="H1" s="94"/>
+      <c r="H1" s="88"/>
       <c r="I1" s="35" t="s">
         <v>136</v>
       </c>
@@ -9894,7 +9894,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="7" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" s="7" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
         <v>144</v>
       </c>
@@ -9944,7 +9944,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>_xlfn.XLOOKUP(B3,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -9983,23 +9983,23 @@
         <f>SUM(J3:K5)</f>
         <v>144</v>
       </c>
-      <c r="M3" s="91" t="s">
+      <c r="M3" s="86" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="91" t="s">
+      <c r="N3" s="86" t="s">
         <v>163</v>
       </c>
-      <c r="O3" s="85" t="s">
+      <c r="O3" s="82" t="s">
         <v>164</v>
       </c>
-      <c r="P3" s="91" t="s">
+      <c r="P3" s="86" t="s">
         <v>165</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="str">
         <f>_xlfn.XLOOKUP(B4,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -10017,12 +10017,12 @@
       <c r="J4" s="79"/>
       <c r="K4" s="79"/>
       <c r="L4" s="79"/>
-      <c r="M4" s="91"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="85"/>
-      <c r="P4" s="91"/>
-    </row>
-    <row r="5" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="M4" s="86"/>
+      <c r="N4" s="86"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="86"/>
+    </row>
+    <row r="5" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="str">
         <f>_xlfn.XLOOKUP(B5,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -10040,12 +10040,12 @@
       <c r="J5" s="80"/>
       <c r="K5" s="80"/>
       <c r="L5" s="80"/>
-      <c r="M5" s="92"/>
-      <c r="N5" s="92"/>
-      <c r="O5" s="86"/>
-      <c r="P5" s="92"/>
-    </row>
-    <row r="6" spans="1:17" ht="66" x14ac:dyDescent="0.5">
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="83"/>
+      <c r="P5" s="85"/>
+    </row>
+    <row r="6" spans="1:17" ht="72" x14ac:dyDescent="0.5">
       <c r="A6" s="27" t="str">
         <f>_xlfn.XLOOKUP(B6,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -10059,7 +10059,7 @@
       <c r="D6" s="72" t="s">
         <v>166</v>
       </c>
-      <c r="E6" s="95" t="s">
+      <c r="E6" s="89" t="s">
         <v>167</v>
       </c>
       <c r="F6" s="72" t="s">
@@ -10084,20 +10084,20 @@
         <f>SUM(J6:K7)</f>
         <v>144</v>
       </c>
-      <c r="M6" s="90" t="s">
+      <c r="M6" s="84" t="s">
         <v>168</v>
       </c>
-      <c r="N6" s="90" t="s">
+      <c r="N6" s="84" t="s">
         <v>163</v>
       </c>
-      <c r="O6" s="84" t="s">
+      <c r="O6" s="81" t="s">
         <v>169</v>
       </c>
-      <c r="P6" s="90" t="s">
+      <c r="P6" s="84" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="49.5" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:17" ht="54" x14ac:dyDescent="0.5">
       <c r="A7" s="26" t="str">
         <f>_xlfn.XLOOKUP(B7,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
-      <c r="E7" s="96"/>
+      <c r="E7" s="90"/>
       <c r="F7" s="74"/>
       <c r="G7" s="80"/>
       <c r="H7" s="80"/>
@@ -10115,12 +10115,12 @@
       <c r="J7" s="80"/>
       <c r="K7" s="80"/>
       <c r="L7" s="80"/>
-      <c r="M7" s="92"/>
-      <c r="N7" s="92"/>
-      <c r="O7" s="86"/>
-      <c r="P7" s="92"/>
-    </row>
-    <row r="8" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+      <c r="M7" s="85"/>
+      <c r="N7" s="85"/>
+      <c r="O7" s="83"/>
+      <c r="P7" s="85"/>
+    </row>
+    <row r="8" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="str">
         <f>_xlfn.XLOOKUP(B8,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -10159,20 +10159,20 @@
         <f>SUM(J8:K8)</f>
         <v>96</v>
       </c>
-      <c r="M8" s="84" t="s">
+      <c r="M8" s="81" t="s">
         <v>173</v>
       </c>
-      <c r="N8" s="90" t="s">
+      <c r="N8" s="84" t="s">
         <v>174</v>
       </c>
-      <c r="O8" s="84" t="s">
+      <c r="O8" s="81" t="s">
         <v>169</v>
       </c>
-      <c r="P8" s="90" t="s">
+      <c r="P8" s="84" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="str">
         <f>_xlfn.XLOOKUP(B9,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -10190,12 +10190,12 @@
       <c r="J9" s="79"/>
       <c r="K9" s="79"/>
       <c r="L9" s="79"/>
-      <c r="M9" s="85"/>
-      <c r="N9" s="91"/>
-      <c r="O9" s="85"/>
-      <c r="P9" s="91"/>
-    </row>
-    <row r="10" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="M9" s="82"/>
+      <c r="N9" s="86"/>
+      <c r="O9" s="82"/>
+      <c r="P9" s="86"/>
+    </row>
+    <row r="10" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A10" s="26" t="str">
         <f>_xlfn.XLOOKUP(B10,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -10213,12 +10213,12 @@
       <c r="J10" s="80"/>
       <c r="K10" s="80"/>
       <c r="L10" s="80"/>
-      <c r="M10" s="86"/>
-      <c r="N10" s="92"/>
-      <c r="O10" s="86"/>
-      <c r="P10" s="92"/>
-    </row>
-    <row r="11" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+      <c r="M10" s="83"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="83"/>
+      <c r="P10" s="85"/>
+    </row>
+    <row r="11" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="str">
         <f>_xlfn.XLOOKUP(B11,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -10263,14 +10263,14 @@
       <c r="N11" s="75" t="s">
         <v>174</v>
       </c>
-      <c r="O11" s="84" t="s">
+      <c r="O11" s="81" t="s">
         <v>177</v>
       </c>
-      <c r="P11" s="90" t="s">
+      <c r="P11" s="84" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A12" s="26" t="str">
         <f>_xlfn.XLOOKUP(B12,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -10290,10 +10290,10 @@
       <c r="L12" s="80"/>
       <c r="M12" s="77"/>
       <c r="N12" s="77"/>
-      <c r="O12" s="86"/>
-      <c r="P12" s="92"/>
-    </row>
-    <row r="13" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+      <c r="O12" s="83"/>
+      <c r="P12" s="85"/>
+    </row>
+    <row r="13" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="str">
         <f>_xlfn.XLOOKUP(B13,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -10317,7 +10317,7 @@
       <c r="H13" s="78" t="s">
         <v>161</v>
       </c>
-      <c r="I13" s="81">
+      <c r="I13" s="94">
         <v>2</v>
       </c>
       <c r="J13" s="78">
@@ -10332,20 +10332,20 @@
         <f>SUM(J13:K15)</f>
         <v>96</v>
       </c>
-      <c r="M13" s="87" t="s">
+      <c r="M13" s="91" t="s">
         <v>180</v>
       </c>
       <c r="N13" s="75" t="s">
         <v>163</v>
       </c>
-      <c r="O13" s="84" t="s">
+      <c r="O13" s="81" t="s">
         <v>169</v>
       </c>
       <c r="P13" s="75" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="str">
         <f>_xlfn.XLOOKUP(B14,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -10359,16 +10359,16 @@
       <c r="F14" s="73"/>
       <c r="G14" s="73"/>
       <c r="H14" s="79"/>
-      <c r="I14" s="82"/>
+      <c r="I14" s="95"/>
       <c r="J14" s="79"/>
       <c r="K14" s="79"/>
       <c r="L14" s="79"/>
-      <c r="M14" s="88"/>
+      <c r="M14" s="92"/>
       <c r="N14" s="76"/>
-      <c r="O14" s="85"/>
+      <c r="O14" s="82"/>
       <c r="P14" s="76"/>
     </row>
-    <row r="15" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A15" s="26" t="str">
         <f>_xlfn.XLOOKUP(B15,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -10382,16 +10382,16 @@
       <c r="F15" s="74"/>
       <c r="G15" s="74"/>
       <c r="H15" s="80"/>
-      <c r="I15" s="83"/>
+      <c r="I15" s="96"/>
       <c r="J15" s="80"/>
       <c r="K15" s="80"/>
       <c r="L15" s="80"/>
-      <c r="M15" s="89"/>
+      <c r="M15" s="93"/>
       <c r="N15" s="77"/>
-      <c r="O15" s="86"/>
+      <c r="O15" s="83"/>
       <c r="P15" s="77"/>
     </row>
-    <row r="16" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="str">
         <f>_xlfn.XLOOKUP(B16,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -10436,14 +10436,14 @@
       <c r="N16" s="75" t="s">
         <v>163</v>
       </c>
-      <c r="O16" s="84" t="s">
+      <c r="O16" s="81" t="s">
         <v>164</v>
       </c>
       <c r="P16" s="75" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" ht="54" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="str">
         <f>_xlfn.XLOOKUP(B17,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -10463,10 +10463,10 @@
       <c r="L17" s="73"/>
       <c r="M17" s="76"/>
       <c r="N17" s="76"/>
-      <c r="O17" s="85"/>
+      <c r="O17" s="82"/>
       <c r="P17" s="76"/>
     </row>
-    <row r="18" spans="1:16" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" ht="54" x14ac:dyDescent="0.3">
       <c r="A18" s="26" t="str">
         <f>_xlfn.XLOOKUP(B18,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -10486,10 +10486,10 @@
       <c r="L18" s="74"/>
       <c r="M18" s="77"/>
       <c r="N18" s="77"/>
-      <c r="O18" s="86"/>
+      <c r="O18" s="83"/>
       <c r="P18" s="77"/>
     </row>
-    <row r="19" spans="1:16" ht="66" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="str">
         <f>_xlfn.XLOOKUP(B19,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -10534,14 +10534,14 @@
       <c r="N19" s="75" t="s">
         <v>163</v>
       </c>
-      <c r="O19" s="84" t="s">
+      <c r="O19" s="81" t="s">
         <v>164</v>
       </c>
       <c r="P19" s="75" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" ht="54" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="str">
         <f>_xlfn.XLOOKUP(B20,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -10561,10 +10561,10 @@
       <c r="L20" s="79"/>
       <c r="M20" s="76"/>
       <c r="N20" s="76"/>
-      <c r="O20" s="85"/>
+      <c r="O20" s="82"/>
       <c r="P20" s="76"/>
     </row>
-    <row r="21" spans="1:16" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" ht="54" x14ac:dyDescent="0.3">
       <c r="A21" s="26" t="str">
         <f>_xlfn.XLOOKUP(B21,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -10584,10 +10584,10 @@
       <c r="L21" s="80"/>
       <c r="M21" s="77"/>
       <c r="N21" s="77"/>
-      <c r="O21" s="86"/>
+      <c r="O21" s="83"/>
       <c r="P21" s="77"/>
     </row>
-    <row r="22" spans="1:16" ht="66" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="str">
         <f>_xlfn.XLOOKUP(B22,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -10632,14 +10632,14 @@
       <c r="N22" s="75" t="s">
         <v>190</v>
       </c>
-      <c r="O22" s="84" t="s">
+      <c r="O22" s="81" t="s">
         <v>164</v>
       </c>
       <c r="P22" s="75" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" ht="54" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="str">
         <f>_xlfn.XLOOKUP(B23,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -10659,10 +10659,10 @@
       <c r="L23" s="79"/>
       <c r="M23" s="76"/>
       <c r="N23" s="76"/>
-      <c r="O23" s="85"/>
+      <c r="O23" s="82"/>
       <c r="P23" s="76"/>
     </row>
-    <row r="24" spans="1:16" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" ht="54" x14ac:dyDescent="0.3">
       <c r="A24" s="26" t="str">
         <f>_xlfn.XLOOKUP(B24,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -10682,10 +10682,10 @@
       <c r="L24" s="80"/>
       <c r="M24" s="77"/>
       <c r="N24" s="77"/>
-      <c r="O24" s="86"/>
+      <c r="O24" s="83"/>
       <c r="P24" s="77"/>
     </row>
-    <row r="25" spans="1:16" ht="66" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="27" t="str">
         <f>_xlfn.XLOOKUP(B25,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -10730,14 +10730,14 @@
       <c r="N25" s="75" t="s">
         <v>163</v>
       </c>
-      <c r="O25" s="84" t="s">
+      <c r="O25" s="81" t="s">
         <v>169</v>
       </c>
       <c r="P25" s="75" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" ht="54" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="str">
         <f>_xlfn.XLOOKUP(B26,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -10757,10 +10757,10 @@
       <c r="L26" s="79"/>
       <c r="M26" s="76"/>
       <c r="N26" s="76"/>
-      <c r="O26" s="85"/>
+      <c r="O26" s="82"/>
       <c r="P26" s="76"/>
     </row>
-    <row r="27" spans="1:16" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" ht="54" x14ac:dyDescent="0.3">
       <c r="A27" s="26" t="str">
         <f>_xlfn.XLOOKUP(B27,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -10780,10 +10780,10 @@
       <c r="L27" s="80"/>
       <c r="M27" s="77"/>
       <c r="N27" s="77"/>
-      <c r="O27" s="86"/>
+      <c r="O27" s="83"/>
       <c r="P27" s="77"/>
     </row>
-    <row r="28" spans="1:16" ht="66" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="27" t="str">
         <f>_xlfn.XLOOKUP(B28,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -10828,14 +10828,14 @@
       <c r="N28" s="75" t="s">
         <v>190</v>
       </c>
-      <c r="O28" s="84" t="s">
+      <c r="O28" s="81" t="s">
         <v>164</v>
       </c>
       <c r="P28" s="75" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" ht="54" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="str">
         <f>_xlfn.XLOOKUP(B29,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -10855,10 +10855,10 @@
       <c r="L29" s="79"/>
       <c r="M29" s="76"/>
       <c r="N29" s="76"/>
-      <c r="O29" s="85"/>
+      <c r="O29" s="82"/>
       <c r="P29" s="76"/>
     </row>
-    <row r="30" spans="1:16" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" ht="54" x14ac:dyDescent="0.3">
       <c r="A30" s="26" t="str">
         <f>_xlfn.XLOOKUP(B30,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -10880,10 +10880,10 @@
       <c r="L30" s="80"/>
       <c r="M30" s="77"/>
       <c r="N30" s="77"/>
-      <c r="O30" s="86"/>
+      <c r="O30" s="83"/>
       <c r="P30" s="77"/>
     </row>
-    <row r="31" spans="1:16" ht="33" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" ht="36" x14ac:dyDescent="0.3">
       <c r="C31" s="57" t="s">
         <v>198</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="33" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="36" x14ac:dyDescent="0.3">
       <c r="H32" s="61" t="s">
         <v>200</v>
       </c>
@@ -10908,7 +10908,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="8:9" ht="33" x14ac:dyDescent="0.35">
+    <row r="33" spans="8:9" ht="36" x14ac:dyDescent="0.3">
       <c r="H33" s="61" t="s">
         <v>201</v>
       </c>
@@ -10919,53 +10919,76 @@
     </row>
   </sheetData>
   <mergeCells count="141">
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="J28:J30"/>
-    <mergeCell ref="K28:K30"/>
-    <mergeCell ref="O16:O18"/>
-    <mergeCell ref="P16:P18"/>
-    <mergeCell ref="O13:O15"/>
-    <mergeCell ref="P13:P15"/>
-    <mergeCell ref="N13:N15"/>
-    <mergeCell ref="O19:O21"/>
-    <mergeCell ref="P19:P21"/>
-    <mergeCell ref="L28:L30"/>
-    <mergeCell ref="M28:M30"/>
-    <mergeCell ref="N28:N30"/>
-    <mergeCell ref="O28:O30"/>
-    <mergeCell ref="P28:P30"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="O8:O10"/>
-    <mergeCell ref="P8:P10"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="L8:L10"/>
-    <mergeCell ref="M8:M10"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="K22:K24"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="I25:I27"/>
+    <mergeCell ref="P25:P27"/>
+    <mergeCell ref="O25:O27"/>
+    <mergeCell ref="N25:N27"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="H16:H18"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="L16:L18"/>
+    <mergeCell ref="M16:M18"/>
+    <mergeCell ref="N16:N18"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="O22:O24"/>
+    <mergeCell ref="P22:P24"/>
+    <mergeCell ref="N19:N21"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="M25:M27"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="L13:L15"/>
+    <mergeCell ref="M13:M15"/>
+    <mergeCell ref="M22:M24"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="L19:L21"/>
+    <mergeCell ref="L22:L24"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="L25:L27"/>
+    <mergeCell ref="K25:K27"/>
+    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="M19:M21"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="E11:E12"/>
@@ -10990,76 +11013,53 @@
     <mergeCell ref="K8:K10"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="L13:L15"/>
-    <mergeCell ref="M13:M15"/>
-    <mergeCell ref="M22:M24"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="L19:L21"/>
-    <mergeCell ref="L22:L24"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="L25:L27"/>
-    <mergeCell ref="K25:K27"/>
-    <mergeCell ref="J25:J27"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="M19:M21"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="I25:I27"/>
-    <mergeCell ref="P25:P27"/>
-    <mergeCell ref="O25:O27"/>
-    <mergeCell ref="N25:N27"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="H16:H18"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="L16:L18"/>
-    <mergeCell ref="M16:M18"/>
-    <mergeCell ref="N16:N18"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="O22:O24"/>
-    <mergeCell ref="P22:P24"/>
-    <mergeCell ref="N19:N21"/>
-    <mergeCell ref="G25:G27"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="M25:M27"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="H13:H15"/>
-    <mergeCell ref="I13:I15"/>
-    <mergeCell ref="J13:J15"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="K22:K24"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="L8:L10"/>
+    <mergeCell ref="M8:M10"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="O8:O10"/>
+    <mergeCell ref="P8:P10"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="O16:O18"/>
+    <mergeCell ref="P16:P18"/>
+    <mergeCell ref="O13:O15"/>
+    <mergeCell ref="P13:P15"/>
+    <mergeCell ref="N13:N15"/>
+    <mergeCell ref="O19:O21"/>
+    <mergeCell ref="P19:P21"/>
+    <mergeCell ref="L28:L30"/>
+    <mergeCell ref="M28:M30"/>
+    <mergeCell ref="N28:N30"/>
+    <mergeCell ref="O28:O30"/>
+    <mergeCell ref="P28:P30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="J28:J30"/>
+    <mergeCell ref="K28:K30"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B44" xr:uid="{149936BB-E9F7-467B-9B8A-466861C21273}">
@@ -11075,13 +11075,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E64FCBD-ADC1-40F4-BFE8-98BA12AA9611}">
   <dimension ref="B1:D39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
-    <col min="4" max="4" width="99.26953125" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" customWidth="1"/>
+    <col min="4" max="4" width="99.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="30.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:4" ht="31.2" x14ac:dyDescent="0.5">
       <c r="B1" s="1" t="s">
         <v>202</v>
       </c>
@@ -11089,192 +11089,192 @@
         <v>203</v>
       </c>
     </row>
-    <row r="2" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="14" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="18" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="22" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="26" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="28" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="29" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="30" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="32" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="34" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="34" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="35" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="36" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="36" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="37" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="38" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="38" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B38" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="39" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B39" s="1" t="s">
         <v>49</v>
       </c>
@@ -11290,139 +11290,139 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A97597-49CE-4804-805A-84A20592BE98}">
   <dimension ref="A1:BK108"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="20.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.54296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.81640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="26.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.26953125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" style="1" customWidth="1"/>
-    <col min="12" max="17" width="17.7265625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="22.54296875" style="1" customWidth="1"/>
-    <col min="19" max="33" width="17.453125" style="1" customWidth="1"/>
-    <col min="34" max="36" width="13.1796875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="14.54296875" style="1" customWidth="1"/>
-    <col min="38" max="38" width="23.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.21875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="1" customWidth="1"/>
+    <col min="12" max="17" width="17.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="22.5546875" style="1" customWidth="1"/>
+    <col min="19" max="33" width="17.44140625" style="1" customWidth="1"/>
+    <col min="34" max="36" width="13.21875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5546875" style="1" customWidth="1"/>
+    <col min="38" max="38" width="23.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="18" style="1" customWidth="1"/>
-    <col min="40" max="40" width="20.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="17.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.7265625" style="1" customWidth="1"/>
-    <col min="45" max="45" width="26.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="21.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="24.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="24.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="23.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="22.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="32.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.26953125" style="1" customWidth="1"/>
-    <col min="54" max="54" width="23.81640625" style="1" customWidth="1"/>
-    <col min="55" max="55" width="22.54296875" style="1" customWidth="1"/>
-    <col min="56" max="56" width="21.453125" style="1" customWidth="1"/>
+    <col min="40" max="40" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="21.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="17.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="18.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.77734375" style="1" customWidth="1"/>
+    <col min="45" max="45" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="21.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="24.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="23.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="22.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="32.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.21875" style="1" customWidth="1"/>
+    <col min="54" max="54" width="23.77734375" style="1" customWidth="1"/>
+    <col min="55" max="55" width="22.5546875" style="1" customWidth="1"/>
+    <col min="56" max="56" width="21.44140625" style="1" customWidth="1"/>
     <col min="57" max="57" width="25" style="1" customWidth="1"/>
-    <col min="58" max="58" width="24.7265625" style="1" customWidth="1"/>
-    <col min="59" max="59" width="22.7265625" style="1" customWidth="1"/>
-    <col min="60" max="63" width="13.26953125" style="1" customWidth="1"/>
-    <col min="64" max="16384" width="11.453125" style="1"/>
+    <col min="58" max="58" width="24.77734375" style="1" customWidth="1"/>
+    <col min="59" max="59" width="22.77734375" style="1" customWidth="1"/>
+    <col min="60" max="63" width="13.21875" style="1" customWidth="1"/>
+    <col min="64" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.5">
-      <c r="S1" s="111" t="s">
+      <c r="S1" s="108" t="s">
         <v>237</v>
       </c>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
-      <c r="V1" s="111"/>
-      <c r="W1" s="111"/>
-      <c r="X1" s="111"/>
-      <c r="Y1" s="111"/>
-      <c r="Z1" s="111"/>
-      <c r="AA1" s="111"/>
-      <c r="AB1" s="111"/>
-      <c r="AC1" s="111"/>
-      <c r="AD1" s="111"/>
-      <c r="AE1" s="111"/>
-      <c r="AF1" s="111"/>
-      <c r="AG1" s="111"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
+      <c r="Z1" s="108"/>
+      <c r="AA1" s="108"/>
+      <c r="AB1" s="108"/>
+      <c r="AC1" s="108"/>
+      <c r="AD1" s="108"/>
+      <c r="AE1" s="108"/>
+      <c r="AF1" s="108"/>
+      <c r="AG1" s="108"/>
       <c r="AH1" s="9"/>
       <c r="AI1" s="9"/>
       <c r="AJ1" s="9"/>
-      <c r="AL1" s="111" t="s">
+      <c r="AL1" s="108" t="s">
         <v>238</v>
       </c>
-      <c r="AM1" s="111"/>
-      <c r="AN1" s="111"/>
-      <c r="AO1" s="111"/>
-      <c r="AP1" s="111"/>
-      <c r="AQ1" s="111"/>
-      <c r="AR1" s="111"/>
-      <c r="AS1" s="111"/>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
+      <c r="AM1" s="108"/>
+      <c r="AN1" s="108"/>
+      <c r="AO1" s="108"/>
+      <c r="AP1" s="108"/>
+      <c r="AQ1" s="108"/>
+      <c r="AR1" s="108"/>
+      <c r="AS1" s="108"/>
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
       <c r="BA1" s="9"/>
-      <c r="BB1" s="111" t="s">
+      <c r="BB1" s="108" t="s">
         <v>239</v>
       </c>
-      <c r="BC1" s="111"/>
-      <c r="BD1" s="111"/>
-      <c r="BE1" s="111"/>
-      <c r="BF1" s="111"/>
-      <c r="BG1" s="111"/>
+      <c r="BC1" s="108"/>
+      <c r="BD1" s="108"/>
+      <c r="BE1" s="108"/>
+      <c r="BF1" s="108"/>
+      <c r="BG1" s="108"/>
       <c r="BH1" s="9"/>
       <c r="BK1" s="9"/>
     </row>
     <row r="2" spans="1:63" x14ac:dyDescent="0.5">
-      <c r="L2" s="111" t="s">
+      <c r="L2" s="108" t="s">
         <v>240</v>
       </c>
-      <c r="M2" s="111"/>
-      <c r="N2" s="111"/>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="S2" s="112" t="s">
+      <c r="M2" s="108"/>
+      <c r="N2" s="108"/>
+      <c r="O2" s="108"/>
+      <c r="P2" s="108"/>
+      <c r="Q2" s="108"/>
+      <c r="S2" s="109" t="s">
         <v>241</v>
       </c>
-      <c r="T2" s="112"/>
-      <c r="U2" s="112"/>
-      <c r="V2" s="112"/>
-      <c r="W2" s="112"/>
-      <c r="X2" s="112"/>
-      <c r="Y2" s="112" t="s">
+      <c r="T2" s="109"/>
+      <c r="U2" s="109"/>
+      <c r="V2" s="109"/>
+      <c r="W2" s="109"/>
+      <c r="X2" s="109"/>
+      <c r="Y2" s="109" t="s">
         <v>242</v>
       </c>
-      <c r="Z2" s="112"/>
-      <c r="AA2" s="112"/>
-      <c r="AB2" s="112"/>
-      <c r="AC2" s="112" t="s">
+      <c r="Z2" s="109"/>
+      <c r="AA2" s="109"/>
+      <c r="AB2" s="109"/>
+      <c r="AC2" s="109" t="s">
         <v>243</v>
       </c>
-      <c r="AD2" s="112"/>
-      <c r="AE2" s="112"/>
-      <c r="AF2" s="112"/>
-      <c r="AG2" s="112"/>
+      <c r="AD2" s="109"/>
+      <c r="AE2" s="109"/>
+      <c r="AF2" s="109"/>
+      <c r="AG2" s="109"/>
       <c r="AH2" s="9"/>
       <c r="AI2" s="9"/>
       <c r="AJ2" s="9"/>
-      <c r="AL2" s="111"/>
-      <c r="AM2" s="111"/>
-      <c r="AN2" s="111"/>
-      <c r="AO2" s="111"/>
-      <c r="AP2" s="111"/>
-      <c r="AQ2" s="111"/>
+      <c r="AL2" s="108"/>
+      <c r="AM2" s="108"/>
+      <c r="AN2" s="108"/>
+      <c r="AO2" s="108"/>
+      <c r="AP2" s="108"/>
+      <c r="AQ2" s="108"/>
       <c r="AR2" s="9"/>
       <c r="AS2" s="9"/>
       <c r="AT2" s="9"/>
@@ -11527,29 +11527,29 @@
       <c r="AG3" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="AL3" s="108" t="s">
+      <c r="AL3" s="110" t="s">
         <v>266</v>
       </c>
-      <c r="AM3" s="109"/>
-      <c r="AN3" s="109"/>
-      <c r="AO3" s="108" t="s">
+      <c r="AM3" s="111"/>
+      <c r="AN3" s="111"/>
+      <c r="AO3" s="110" t="s">
         <v>267</v>
       </c>
-      <c r="AP3" s="109"/>
-      <c r="AQ3" s="109"/>
-      <c r="AR3" s="108" t="s">
+      <c r="AP3" s="111"/>
+      <c r="AQ3" s="111"/>
+      <c r="AR3" s="110" t="s">
         <v>268</v>
       </c>
-      <c r="AS3" s="109"/>
-      <c r="AT3" s="109"/>
-      <c r="AU3" s="110"/>
-      <c r="AV3" s="108" t="s">
+      <c r="AS3" s="111"/>
+      <c r="AT3" s="111"/>
+      <c r="AU3" s="112"/>
+      <c r="AV3" s="110" t="s">
         <v>269</v>
       </c>
-      <c r="AW3" s="109"/>
-      <c r="AX3" s="109"/>
-      <c r="AY3" s="109"/>
-      <c r="AZ3" s="110"/>
+      <c r="AW3" s="111"/>
+      <c r="AX3" s="111"/>
+      <c r="AY3" s="111"/>
+      <c r="AZ3" s="112"/>
       <c r="BA3" s="10"/>
       <c r="BB3" s="10"/>
       <c r="BC3" s="10"/>
@@ -17598,11 +17598,6 @@
     <sortCondition ref="BC5:BC66"/>
   </sortState>
   <mergeCells count="12">
-    <mergeCell ref="S1:AG1"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="S2:X2"/>
-    <mergeCell ref="Y2:AB2"/>
-    <mergeCell ref="AC2:AG2"/>
     <mergeCell ref="AV3:AZ3"/>
     <mergeCell ref="AR3:AU3"/>
     <mergeCell ref="AL3:AN3"/>
@@ -17610,6 +17605,11 @@
     <mergeCell ref="BB1:BG1"/>
     <mergeCell ref="AL2:AQ2"/>
     <mergeCell ref="AL1:AZ1"/>
+    <mergeCell ref="S1:AG1"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="Y2:AB2"/>
+    <mergeCell ref="AC2:AG2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17675,26 +17675,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5fb26c54-8ae7-4c35-a8dd-e5095fbe886d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91d06b0e-e43f-423b-9ab9-9a6b45a2a239" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009AC520CAB569B54B8400FCA196E34CBB" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0d3609084ddb063b5cee30209fffb50e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5fb26c54-8ae7-4c35-a8dd-e5095fbe886d" xmlns:ns3="91d06b0e-e43f-423b-9ab9-9a6b45a2a239" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9a35c40912acb536c870627743568d9d" ns2:_="" ns3:_="">
     <xsd:import namespace="5fb26c54-8ae7-4c35-a8dd-e5095fbe886d"/>
@@ -17889,26 +17869,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9F25991-7111-4C83-98CC-569D7D2F527C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5fb26c54-8ae7-4c35-a8dd-e5095fbe886d"/>
-    <ds:schemaRef ds:uri="91d06b0e-e43f-423b-9ab9-9a6b45a2a239"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE715072-900F-43EC-BD52-E1C5E784E778}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5fb26c54-8ae7-4c35-a8dd-e5095fbe886d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91d06b0e-e43f-423b-9ab9-9a6b45a2a239" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9493F5F7-D611-49DF-808E-AFE6C09CB650}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17925,4 +17906,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE715072-900F-43EC-BD52-E1C5E784E778}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9F25991-7111-4C83-98CC-569D7D2F527C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5fb26c54-8ae7-4c35-a8dd-e5095fbe886d"/>
+    <ds:schemaRef ds:uri="91d06b0e-e43f-423b-9ab9-9a6b45a2a239"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>